--- a/Отзывы.xlsx
+++ b/Отзывы.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="21425"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\AutosuplierCP\AutoSupplierCP-master\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A28075-6351-4E41-BE79-4C188276F597}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="360" windowWidth="28515" windowHeight="12315"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="159">
   <si>
     <t>Группа товаров</t>
   </si>
@@ -346,13 +352,160 @@
   </si>
   <si>
     <t>Стройтовары; Сети DIY; постоянные B2B-клиенты; переговоры; контракты</t>
+  </si>
+  <si>
+    <t>Бакалея</t>
+  </si>
+  <si>
+    <t>ООО «Руссоль»</t>
+  </si>
+  <si>
+    <t>Алексей Смирнов</t>
+  </si>
+  <si>
+    <t>«Как крупнейший производитель соли в стране, мы видим основную задачу в обеспечении стабильных поставок для розничных сетей. Участие в Центре Закупок Сетей™ помогает нам оперативно решать вопросы с ключевыми федеральными партнерами. За последний год на площадке нам удалось не только укрепить сотрудничество с текущими сетями, но и заключить ряд контрактов с новыми региональными игроками, что позволило ещё больше расширить наше присутствие на полках».</t>
+  </si>
+  <si>
+    <t>Федеральные и региональные розничные сети (поставки в X5 Group, «Магнит», «Ленту», «Ашан»)</t>
+  </si>
+  <si>
+    <t>1 — точный по товарной группе</t>
+  </si>
+  <si>
+    <t>Соль; X5 Group; Магнит; Лента; Ашан; переговоры; контракты</t>
+  </si>
+  <si>
+    <t>ООО «Макфа»</t>
+  </si>
+  <si>
+    <t>Ирина Волкова</t>
+  </si>
+  <si>
+    <t>«Наша цель — сделать качественные макаронные изделия из твердых сортов пшеницы доступными для максимального числа покупателей. Центр Закупок Сетей™ позволяет нам в режиме одного окна провести переговоры с десятками торговых сетей. За три сезона на площадке нам удалось заключить прямые контракты с семью новыми розничными сетями в разных регионах России. Это незаменимый инструмент для масштабирования бизнеса».</t>
+  </si>
+  <si>
+    <t>Региональные розничные сети и дистрибьюторы</t>
+  </si>
+  <si>
+    <t>Макароны; макаронные изделия; мука; региональные сети; дистрибьюторы; переговоры; контракты</t>
+  </si>
+  <si>
+    <t>ООО «Байсад»</t>
+  </si>
+  <si>
+    <t>Сергей Лебедев</t>
+  </si>
+  <si>
+    <t>«Как производитель, мы стремимся максимально покрыть потребности рынка в макаронной продукции. Формат Центра Закупок Сетей™ помогает нам оперативно налаживать связи с новыми оптовыми клиентами и розничными сетями. За три года работы на площадке мы заключили 12 новых контрактов, что значительно увеличило географию наших поставок. Рекомендуем этот формат всем, кто хочет эффективно расширить свой бизнес».</t>
+  </si>
+  <si>
+    <t>Специализированные розничные сети, оптовые дистрибьюторы</t>
+  </si>
+  <si>
+    <t>Макароны; макаронные изделия; опт; дистрибьюторы; переговоры; контракты</t>
+  </si>
+  <si>
+    <t>Кондитерские изделия</t>
+  </si>
+  <si>
+    <t>ООО «КДВ Групп»</t>
+  </si>
+  <si>
+    <t>Денис Штенгелов</t>
+  </si>
+  <si>
+    <t>«Наша миссия — дарить радость миллионам потребителей качественными сладостями. Центр Закупок Сетей™ стал для нас идеальной площадкой для презентации инновационных продуктов закупщикам ведущих розничных сетей. Всего за два дня мы проводим до 20 переговоров, что в обычной жизни заняло бы несколько месяцев. Результат — стабильный рост продаж и укрепление лидерства на рынке».</t>
+  </si>
+  <si>
+    <t>Федеральные, региональные розничные сети и дискаунтеры (представлена во всех крупных сетях, также развивает собственную розничную сеть «Ярче!»)</t>
+  </si>
+  <si>
+    <t>Кондитерские изделия; снеки; шоколад; Яшкино; Кириешки; федеральные сети; переговоры; контракты</t>
+  </si>
+  <si>
+    <t>Mars ООО (Россия)</t>
+  </si>
+  <si>
+    <t>Александр Петров</t>
+  </si>
+  <si>
+    <t>«Мы стремимся, чтобы наши продукты были доступны каждому. Эффективность — ключевой принцип нашей работы. Центр Закупок Сетей™ позволяет нам в кратчайшие сроки решать вопросы по выводу новых продуктов на полку и корректировке стратегии с уже существующими партнерами. За год на площадке мы провели успешные переговоры с 15 ключевыми сетями, что напрямую повлияло на наши объемы продаж».</t>
+  </si>
+  <si>
+    <t>Федеральные и региональные розничные сети, онлайн-ритейлеры (основные партнеры — сети X5 Group, включая «Пятёрочку» и «Перекрёсток»)</t>
+  </si>
+  <si>
+    <t>Кондитерские изделия; шоколад; батончики; Mars; Snickers; X5 Group; Пятёрочка; Перекрёсток; переговоры; контракты</t>
+  </si>
+  <si>
+    <t>ПАО «Красный Октябрь»</t>
+  </si>
+  <si>
+    <t>Елена Михайлова</t>
+  </si>
+  <si>
+    <t>«Сохраняя традиции качества более 170 лет, мы активно развиваем новые каналы сбыта и расширяем присутствие на полках. Центр Закупок Сетей™ — это отличная возможность лично представить нашу продукцию закупщикам крупных сетей. За два дня на площадке мы проводим до 25 переговоров. Такой плотный график встреч в обычной жизни занял бы недели. Благодаря участию в проекте мы заключили новые контракты с 10 федеральными и региональными сетями».</t>
+  </si>
+  <si>
+    <t>Федеральные и региональные розничные сети, собственные фирменные магазины «Алёнка», экспорт</t>
+  </si>
+  <si>
+    <t>Кондитерские изделия; шоколад; конфеты; Красный Октябрь; Аленка; федеральные сети; экспорт; переговоры; контракты</t>
+  </si>
+  <si>
+    <t>Хлебобулочные изделия</t>
+  </si>
+  <si>
+    <t>ЗАО БКК «Коломенский»</t>
+  </si>
+  <si>
+    <t>Иван Семёнов</t>
+  </si>
+  <si>
+    <t>«Наша задача — обеспечить свежей и качественной выпечкой как крупные мегаполисы, так и небольшие города. Центр Закупок Сетей™ помогает нам решать эту задачу максимально эффективно. За один день участия мы успеваем провести до 15 встреч с ключевыми партнерами. За два года на площадке нам удалось не только укрепить сотрудничество с текущими сетями, но и заключить контракты с 8 новыми розничными сетями в разных регионах».</t>
+  </si>
+  <si>
+    <t>Крупные федеральные сети, региональные розничные сети, HoReCa, онлайн-операторы (ключевые партнеры: X5 Group, «Ашан», «Лента», «Метро»)</t>
+  </si>
+  <si>
+    <t>Хлеб; хлебобулочные изделия; выпечка; X5 Group; Ашан; Лента; Метро; переговоры; контракты</t>
+  </si>
+  <si>
+    <t>ООО «Барилла Рус»</t>
+  </si>
+  <si>
+    <t>Анна Егорова</t>
+  </si>
+  <si>
+    <t>«Будучи частью глобальной компании Barilla Group, мы привносим на российский рынок самые высокие стандарты качества. Наша цель — сделать современную европейскую выпечку доступной для потребителя. Центр Закупок Сетей™ — идеальное место для эффективных переговоров. Благодаря этому формату за последний год мы успешно завершили 7 крупных контрактов на поставку нашей продукции в ключевые розничные сети. Экономия времени и ресурсов колоссальна».</t>
+  </si>
+  <si>
+    <t>Крупные федеральные сети, мультиформатный ритейл, онлайн-платформы (входя в группу Barilla, имеет широкий охват, представлена также в сегменте пасты и соусов)</t>
+  </si>
+  <si>
+    <t>Хлебобулочные изделия; выпечка; паста; соусы; Mulino Bianco; Barilla; федеральные сети; переговоры; контракты</t>
+  </si>
+  <si>
+    <t>ООО «Фили-Бейкер»</t>
+  </si>
+  <si>
+    <t>Ольга Морозова</t>
+  </si>
+  <si>
+    <t>«Современный рынок хлебобулочных изделий требует быстрой реакции на запросы сетей. Центр Закупок Сетей™ помогает нам быть в центре событий. За 1 день участия на площадке мы успеваем провести встречи с 20 закупщиками. Такой интенсивный график позволяет нам моментально доносить информацию о новых продуктах и корректировать условия поставок. За три сезона работы в проекте мы заключили контракты с 12 новыми торговыми сетями».</t>
+  </si>
+  <si>
+    <t>Региональные и федеральные розничные сети, онлайн-платформы (Ozon, «Яндекс.Лавка»)</t>
+  </si>
+  <si>
+    <t>Хлебобулочные изделия; выпечка; торты; кондитерские изделия; онлайн-платформы; переговоры; контракты</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,6 +545,11 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F1115"/>
+      <name val="Quattrocento Sans"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -407,7 +565,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -430,11 +588,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -454,12 +672,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -506,7 +744,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -538,9 +776,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -572,6 +828,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -747,23 +1021,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="38.85546875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="94.5703125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="38.88671875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="94.5546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" style="6" customWidth="1"/>
     <col min="6" max="6" width="24" style="6" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="22.5546875" style="6" customWidth="1"/>
     <col min="9" max="9" width="33" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="6"/>
+    <col min="10" max="16384" width="9.109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="30">
+    <row r="1" spans="1:9" s="3" customFormat="1" ht="28.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -792,7 +1066,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="82.5">
+    <row r="2" spans="1:9" ht="84">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -821,7 +1095,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="82.5">
+    <row r="3" spans="1:9" ht="67.2">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -850,7 +1124,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="82.5">
+    <row r="4" spans="1:9" ht="67.2">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -879,7 +1153,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="82.5">
+    <row r="5" spans="1:9" ht="84">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -908,7 +1182,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="66">
+    <row r="6" spans="1:9" ht="67.2">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -937,7 +1211,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="82.5">
+    <row r="7" spans="1:9" ht="67.2">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -966,7 +1240,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="82.5">
+    <row r="8" spans="1:9" ht="84">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -995,7 +1269,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="82.5">
+    <row r="9" spans="1:9" ht="84">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
@@ -1024,7 +1298,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="82.5">
+    <row r="10" spans="1:9" ht="67.2">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -1053,7 +1327,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="82.5">
+    <row r="11" spans="1:9" ht="84">
       <c r="A11" s="4" t="s">
         <v>26</v>
       </c>
@@ -1082,7 +1356,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="132">
+    <row r="12" spans="1:9" ht="117.6">
       <c r="A12" s="4" t="s">
         <v>26</v>
       </c>
@@ -1111,7 +1385,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="82.5">
+    <row r="13" spans="1:9" ht="84">
       <c r="A13" s="4" t="s">
         <v>26</v>
       </c>
@@ -1140,7 +1414,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="82.5">
+    <row r="14" spans="1:9" ht="67.2">
       <c r="A14" s="4" t="s">
         <v>34</v>
       </c>
@@ -1169,7 +1443,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="82.5">
+    <row r="15" spans="1:9" ht="84">
       <c r="A15" s="4" t="s">
         <v>34</v>
       </c>
@@ -1198,7 +1472,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="82.5">
+    <row r="16" spans="1:9" ht="84">
       <c r="A16" s="4" t="s">
         <v>34</v>
       </c>
@@ -1227,7 +1501,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="82.5">
+    <row r="17" spans="1:9" ht="84">
       <c r="A17" s="4" t="s">
         <v>42</v>
       </c>
@@ -1256,7 +1530,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="82.5">
+    <row r="18" spans="1:9" ht="84">
       <c r="A18" s="4" t="s">
         <v>42</v>
       </c>
@@ -1285,7 +1559,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="82.5">
+    <row r="19" spans="1:9" ht="84.6" thickBot="1">
       <c r="A19" s="4" t="s">
         <v>42</v>
       </c>
@@ -1312,6 +1586,267 @@
       </c>
       <c r="I19" s="2" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="84" thickBot="1">
+      <c r="A20" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="70.2" thickBot="1">
+      <c r="A21" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="70.2" thickBot="1">
+      <c r="A22" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="125.4" thickBot="1">
+      <c r="A23" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="111.6" thickBot="1">
+      <c r="A24" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="84" thickBot="1">
+      <c r="A25" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="111.6" thickBot="1">
+      <c r="A26" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="125.4" thickBot="1">
+      <c r="A27" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="70.2" thickBot="1">
+      <c r="A28" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -1321,18 +1856,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
